--- a/reports/一级子公司A_现金流量表_2026-06.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-06.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>127435308</v>
+        <v>126486116</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>858609648</v>
+        <v>846751016</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3072807</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>17438920</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1549828</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>8713398</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>767408</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>4358797</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>619939</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3486282</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>460911</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2614528</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>309377</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1743628</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>231064</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1306947</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>154215</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>871973</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>386337</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>2178025</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>193181</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1095565</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>123135</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>692557</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>403142</v>
+        <v>395641</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2277948</v>
+        <v>2247116</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2864430</v>
+        <v>2841413</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>16185420</v>
+        <v>15973755</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>130702880</v>
+        <v>137591372</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>101846400</v>
+        <v>100502797</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>575481600</v>
+        <v>567201664</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1025977</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>5813304</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>774044</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>4356204</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>511851</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2906326</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>387547</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>2178521</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>255830</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1452800</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>194640</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1095155</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16656130</v>
+        <v>16379929</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>94115220</v>
+        <v>92839714</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8487200</v>
+        <v>8385606</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>47956800</v>
+        <v>47308319</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3500970</v>
+        <v>3453532</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>19782180</v>
+        <v>19512411</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>130490700</v>
+        <v>131871753</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>212180</v>
+        <v>5719619</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>182266</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1112400</v>
+        <v>1098090</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1521882</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>9270000</v>
+        <v>9142795</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>934798</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>5685600</v>
+        <v>5611257</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1704148</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14134721</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>86520000</v>
+        <v>85108126</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2032610</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>12360000</v>
+        <v>12139942</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10085643</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>61800000</v>
+        <v>60828405</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>385074</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2348400</v>
+        <v>2315856</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14519795</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12815647</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3572755</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>21630000</v>
+        <v>21352832</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5617742</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>33990000</v>
+        <v>33530434</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5562621</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>33990000</v>
+        <v>33547147</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>183791</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1112400</v>
+        <v>1097871</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9374288</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4583782</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27810000</v>
+        <v>27452641</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4573417</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>27810000</v>
+        <v>27444668</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>731075</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>4449600</v>
+        <v>4393194</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>637981</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3893400</v>
+        <v>3844295</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91931</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>556200</v>
+        <v>548826</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5406788</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3967500</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>-8882720</v>
+        <v>-3128528</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>-8882720</v>
+        <v>-3128528</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
